--- a/Spettatori.xlsx
+++ b/Spettatori.xlsx
@@ -109,7 +109,7 @@
     <t xml:space="preserve">Incasso totale</t>
   </si>
   <si>
-    <t xml:space="preserve">* percentuale del totale di ogni sala sul totale dei biglietti venduti</t>
+    <t xml:space="preserve">* peso in percentuale del totale di ogni sala sul totale dei biglietti venduti</t>
   </si>
 </sst>
 </file>
@@ -253,144 +253,136 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -584,7 +576,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P23"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.78"/>
@@ -1036,12 +1028,12 @@
       <c r="G16" s="23"/>
       <c r="H16" s="23"/>
       <c r="I16" s="24"/>
-      <c r="L16" s="25" t="s">
+      <c r="L16" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="M16" s="25"/>
-      <c r="N16" s="25"/>
-      <c r="O16" s="26"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="19"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
@@ -1057,7 +1049,7 @@
       <c r="I17" s="24"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="25" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="23"/>
@@ -1068,56 +1060,56 @@
       <c r="G18" s="23"/>
       <c r="H18" s="23"/>
       <c r="I18" s="24"/>
-      <c r="L18" s="28" t="s">
+      <c r="L18" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="M18" s="28"/>
-      <c r="N18" s="29"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="27"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="31"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="29"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="29"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="27"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
       <c r="H20" s="16"/>
       <c r="I20" s="16"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C21" s="33"/>
+      <c r="C21" s="31"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="34" t="s">
+      <c r="A23" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="34"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="18">
